--- a/LoginCPARS/Login-CPARS/Input/Ford Receiving - Input.xlsx
+++ b/LoginCPARS/Login-CPARS/Input/Ford Receiving - Input.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skrishnan1\Videos\Proj\LoginCPARS\Login-CPARS\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CF8E47-099B-45DE-B282-4322190D0926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700514FE-4C55-446D-92F1-269CC5AC2937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79995E57-A43A-43D8-997D-622DCF610173}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Customer PO</t>
   </si>
@@ -87,6 +87,21 @@
   </si>
   <si>
     <t>RL26442649</t>
+  </si>
+  <si>
+    <t>B45RL26720042</t>
+  </si>
+  <si>
+    <t>2488920</t>
+  </si>
+  <si>
+    <t>060ZA2404</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>RL26720042</t>
   </si>
 </sst>
 </file>
@@ -458,7 +473,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B01D7E-9741-4D75-B0F4-F372D4AABE30}">
-  <dimension ref="A1:F3"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -526,6 +542,26 @@
         <v>15</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LoginCPARS/Login-CPARS/Input/Ford Receiving - Input.xlsx
+++ b/LoginCPARS/Login-CPARS/Input/Ford Receiving - Input.xlsx
@@ -8,38 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skrishnan1\Videos\Proj\LoginCPARS\Login-CPARS\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700514FE-4C55-446D-92F1-269CC5AC2937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70446DA-4D1D-4217-8EAF-BB01F1361592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79995E57-A43A-43D8-997D-622DCF610173}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="307">
   <si>
     <t>Customer PO</t>
   </si>
@@ -50,15 +31,6 @@
     <t>Customer Item Number</t>
   </si>
   <si>
-    <t>B43RL25432323</t>
-  </si>
-  <si>
-    <t>2461777</t>
-  </si>
-  <si>
-    <t>032ZA2015</t>
-  </si>
-  <si>
     <t>Div</t>
   </si>
   <si>
@@ -68,53 +40,926 @@
     <t>DOC No</t>
   </si>
   <si>
+    <t>B43PO26446825</t>
+  </si>
+  <si>
+    <t>2507946</t>
+  </si>
+  <si>
+    <t>4812749384</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>43</t>
   </si>
   <si>
-    <t>RL25432323</t>
-  </si>
-  <si>
-    <t>B43RL26442649</t>
-  </si>
-  <si>
-    <t>2492570</t>
-  </si>
-  <si>
-    <t>060ZA2205</t>
-  </si>
-  <si>
-    <t>RL26442649</t>
-  </si>
-  <si>
-    <t>B45RL26720042</t>
-  </si>
-  <si>
-    <t>2488920</t>
-  </si>
-  <si>
-    <t>060ZA2404</t>
+    <t>PO26446825</t>
+  </si>
+  <si>
+    <t>B45RL26723624</t>
+  </si>
+  <si>
+    <t>2500543</t>
+  </si>
+  <si>
+    <t>016ZA19692 1</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>RL26720042</t>
+    <t>RL26723624</t>
+  </si>
+  <si>
+    <t>B45RL26724224</t>
+  </si>
+  <si>
+    <t>2502808</t>
+  </si>
+  <si>
+    <t>034ZA2321 R</t>
+  </si>
+  <si>
+    <t>RL26724224</t>
+  </si>
+  <si>
+    <t>B45RL26724228</t>
+  </si>
+  <si>
+    <t>2502765</t>
+  </si>
+  <si>
+    <t>034ZA2393R</t>
+  </si>
+  <si>
+    <t>RL26724228</t>
+  </si>
+  <si>
+    <t>B45RL26724268</t>
+  </si>
+  <si>
+    <t>2502682</t>
+  </si>
+  <si>
+    <t>036ZA6389 1 R</t>
+  </si>
+  <si>
+    <t>RL26724268</t>
+  </si>
+  <si>
+    <t>B45RL26724373</t>
+  </si>
+  <si>
+    <t>2503213</t>
+  </si>
+  <si>
+    <t>034ZA2357 R</t>
+  </si>
+  <si>
+    <t>RL26724373</t>
+  </si>
+  <si>
+    <t>B45RL26724376</t>
+  </si>
+  <si>
+    <t>2503166</t>
+  </si>
+  <si>
+    <t>034ZA2384R</t>
+  </si>
+  <si>
+    <t>RL26724376</t>
+  </si>
+  <si>
+    <t>B45RL26724380</t>
+  </si>
+  <si>
+    <t>2503179</t>
+  </si>
+  <si>
+    <t>034ZA2395R</t>
+  </si>
+  <si>
+    <t>RL26724380</t>
+  </si>
+  <si>
+    <t>B45RL26724381</t>
+  </si>
+  <si>
+    <t>2503165</t>
+  </si>
+  <si>
+    <t>034ZA2396R</t>
+  </si>
+  <si>
+    <t>RL26724381</t>
+  </si>
+  <si>
+    <t>B45RL26724383</t>
+  </si>
+  <si>
+    <t>2503226</t>
+  </si>
+  <si>
+    <t>034ZA2399R</t>
+  </si>
+  <si>
+    <t>RL26724383</t>
+  </si>
+  <si>
+    <t>B45RL26724384</t>
+  </si>
+  <si>
+    <t>2503183</t>
+  </si>
+  <si>
+    <t>034ZA2400R</t>
+  </si>
+  <si>
+    <t>RL26724384</t>
+  </si>
+  <si>
+    <t>B45RL26724697</t>
+  </si>
+  <si>
+    <t>2504151</t>
+  </si>
+  <si>
+    <t>034ZA2246 R</t>
+  </si>
+  <si>
+    <t>RL26724697</t>
+  </si>
+  <si>
+    <t>B45RL26724703</t>
+  </si>
+  <si>
+    <t>2504142</t>
+  </si>
+  <si>
+    <t>RL26724703</t>
+  </si>
+  <si>
+    <t>B45RL26724704</t>
+  </si>
+  <si>
+    <t>2504150</t>
+  </si>
+  <si>
+    <t>RL26724704</t>
+  </si>
+  <si>
+    <t>B45RL26724986</t>
+  </si>
+  <si>
+    <t>2504726</t>
+  </si>
+  <si>
+    <t>034ZA2165 1 R</t>
+  </si>
+  <si>
+    <t>RL26724986</t>
+  </si>
+  <si>
+    <t>B45RL26724991</t>
+  </si>
+  <si>
+    <t>2504735</t>
+  </si>
+  <si>
+    <t>034ZA2380R</t>
+  </si>
+  <si>
+    <t>RL26724991</t>
+  </si>
+  <si>
+    <t>B45RL26724993</t>
+  </si>
+  <si>
+    <t>2504725</t>
+  </si>
+  <si>
+    <t>034ZA2387R</t>
+  </si>
+  <si>
+    <t>RL26724993</t>
+  </si>
+  <si>
+    <t>B45RL26725615</t>
+  </si>
+  <si>
+    <t>2506305</t>
+  </si>
+  <si>
+    <t>84065388</t>
+  </si>
+  <si>
+    <t>RL26725615</t>
+  </si>
+  <si>
+    <t>B45RL26725643</t>
+  </si>
+  <si>
+    <t>2506682</t>
+  </si>
+  <si>
+    <t>RL26725643</t>
+  </si>
+  <si>
+    <t>B45RL26725692</t>
+  </si>
+  <si>
+    <t>2506991</t>
+  </si>
+  <si>
+    <t>48067607</t>
+  </si>
+  <si>
+    <t>RL26725692</t>
+  </si>
+  <si>
+    <t>B45RL26725723</t>
+  </si>
+  <si>
+    <t>2506986</t>
+  </si>
+  <si>
+    <t>016ZA19693 1</t>
+  </si>
+  <si>
+    <t>RL26725723</t>
+  </si>
+  <si>
+    <t>B45RL26726069</t>
+  </si>
+  <si>
+    <t>2507988</t>
+  </si>
+  <si>
+    <t>0201062</t>
+  </si>
+  <si>
+    <t>RL26726069</t>
+  </si>
+  <si>
+    <t>B45RL26726079</t>
+  </si>
+  <si>
+    <t>2507944</t>
+  </si>
+  <si>
+    <t>84091980</t>
+  </si>
+  <si>
+    <t>RL26726079</t>
+  </si>
+  <si>
+    <t>B48RL26080154</t>
+  </si>
+  <si>
+    <t>2499973</t>
+  </si>
+  <si>
+    <t>1014363101</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>RL26080154</t>
+  </si>
+  <si>
+    <t>B48RL26080156</t>
+  </si>
+  <si>
+    <t>2499976</t>
+  </si>
+  <si>
+    <t>1014363661</t>
+  </si>
+  <si>
+    <t>RL26080156</t>
+  </si>
+  <si>
+    <t>B48RL26081168</t>
+  </si>
+  <si>
+    <t>2504710</t>
+  </si>
+  <si>
+    <t>1014265369R</t>
+  </si>
+  <si>
+    <t>RL26081168</t>
+  </si>
+  <si>
+    <t>B48RL26081711</t>
+  </si>
+  <si>
+    <t>2507039</t>
+  </si>
+  <si>
+    <t>012ZC3062D1R</t>
+  </si>
+  <si>
+    <t>RL26081711</t>
+  </si>
+  <si>
+    <t>B48RL26081712</t>
+  </si>
+  <si>
+    <t>2507040</t>
+  </si>
+  <si>
+    <t>036ZC4878D1R</t>
+  </si>
+  <si>
+    <t>RL26081712</t>
+  </si>
+  <si>
+    <t>B48RL26081774</t>
+  </si>
+  <si>
+    <t>2507321</t>
+  </si>
+  <si>
+    <t>020121019</t>
+  </si>
+  <si>
+    <t>RL26081774</t>
+  </si>
+  <si>
+    <t>B48RL26081836</t>
+  </si>
+  <si>
+    <t>2507702</t>
+  </si>
+  <si>
+    <t>480632716</t>
+  </si>
+  <si>
+    <t>RL26081836</t>
+  </si>
+  <si>
+    <t>B48RL26081920</t>
+  </si>
+  <si>
+    <t>2507695</t>
+  </si>
+  <si>
+    <t>036ZC4834 R</t>
+  </si>
+  <si>
+    <t>RL26081920</t>
+  </si>
+  <si>
+    <t>B48RL26081921</t>
+  </si>
+  <si>
+    <t>2507696</t>
+  </si>
+  <si>
+    <t>36ZC4887D1R</t>
+  </si>
+  <si>
+    <t>RL26081921</t>
+  </si>
+  <si>
+    <t>B48RL26081992</t>
+  </si>
+  <si>
+    <t>2508002</t>
+  </si>
+  <si>
+    <t>012ZC3056 1R</t>
+  </si>
+  <si>
+    <t>RL26081992</t>
+  </si>
+  <si>
+    <t>B48RL26081993</t>
+  </si>
+  <si>
+    <t>2508003</t>
+  </si>
+  <si>
+    <t>RL26081993</t>
+  </si>
+  <si>
+    <t>B48RL26082047</t>
+  </si>
+  <si>
+    <t>2508386</t>
+  </si>
+  <si>
+    <t>840320202 R</t>
+  </si>
+  <si>
+    <t>RL26082047</t>
+  </si>
+  <si>
+    <t>B48RL26082048</t>
+  </si>
+  <si>
+    <t>2508387</t>
+  </si>
+  <si>
+    <t>840320208 R</t>
+  </si>
+  <si>
+    <t>RL26082048</t>
+  </si>
+  <si>
+    <t>B48RL26082049</t>
+  </si>
+  <si>
+    <t>2508388</t>
+  </si>
+  <si>
+    <t>840320800 R</t>
+  </si>
+  <si>
+    <t>RL26082049</t>
+  </si>
+  <si>
+    <t>B48RL26082050</t>
+  </si>
+  <si>
+    <t>2508389</t>
+  </si>
+  <si>
+    <t>840320904 R</t>
+  </si>
+  <si>
+    <t>RL26082050</t>
+  </si>
+  <si>
+    <t>B48RL26082051</t>
+  </si>
+  <si>
+    <t>2508392</t>
+  </si>
+  <si>
+    <t>840320916 R</t>
+  </si>
+  <si>
+    <t>RL26082051</t>
+  </si>
+  <si>
+    <t>B48RL26082052</t>
+  </si>
+  <si>
+    <t>2508393</t>
+  </si>
+  <si>
+    <t>840320918 R</t>
+  </si>
+  <si>
+    <t>RL26082052</t>
+  </si>
+  <si>
+    <t>B48RL26082053</t>
+  </si>
+  <si>
+    <t>2508394</t>
+  </si>
+  <si>
+    <t>840321955 R</t>
+  </si>
+  <si>
+    <t>RL26082053</t>
+  </si>
+  <si>
+    <t>B48RL26082054</t>
+  </si>
+  <si>
+    <t>2508395</t>
+  </si>
+  <si>
+    <t>840322000 R</t>
+  </si>
+  <si>
+    <t>RL26082054</t>
+  </si>
+  <si>
+    <t>B48RL26082055</t>
+  </si>
+  <si>
+    <t>2508397</t>
+  </si>
+  <si>
+    <t>840322041 R</t>
+  </si>
+  <si>
+    <t>RL26082055</t>
+  </si>
+  <si>
+    <t>B48RL26082056</t>
+  </si>
+  <si>
+    <t>2508398</t>
+  </si>
+  <si>
+    <t>840329710 R</t>
+  </si>
+  <si>
+    <t>RL26082056</t>
+  </si>
+  <si>
+    <t>B48RL26082057</t>
+  </si>
+  <si>
+    <t>2508400</t>
+  </si>
+  <si>
+    <t>840323259R</t>
+  </si>
+  <si>
+    <t>RL26082057</t>
+  </si>
+  <si>
+    <t>B48RL26082058</t>
+  </si>
+  <si>
+    <t>2508401</t>
+  </si>
+  <si>
+    <t>840325771R</t>
+  </si>
+  <si>
+    <t>RL26082058</t>
+  </si>
+  <si>
+    <t>B48RL26082059</t>
+  </si>
+  <si>
+    <t>2508403</t>
+  </si>
+  <si>
+    <t>840325773R</t>
+  </si>
+  <si>
+    <t>RL26082059</t>
+  </si>
+  <si>
+    <t>B49RL26354859</t>
+  </si>
+  <si>
+    <t>2506683</t>
+  </si>
+  <si>
+    <t>036ZX36801R</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>RL26354859</t>
+  </si>
+  <si>
+    <t>B61RL26386551</t>
+  </si>
+  <si>
+    <t>2503691</t>
+  </si>
+  <si>
+    <t>62077183</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>RL26386551</t>
+  </si>
+  <si>
+    <t>B63RL26509014</t>
+  </si>
+  <si>
+    <t>2494915</t>
+  </si>
+  <si>
+    <t>5ZE8582D5</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>RL26509014</t>
+  </si>
+  <si>
+    <t>B63RL26509027</t>
+  </si>
+  <si>
+    <t>2494894</t>
+  </si>
+  <si>
+    <t>43ZE921D2</t>
+  </si>
+  <si>
+    <t>RL26509027</t>
+  </si>
+  <si>
+    <t>B63RL26511088</t>
+  </si>
+  <si>
+    <t>2505318</t>
+  </si>
+  <si>
+    <t>5ZE8427D4</t>
+  </si>
+  <si>
+    <t>RL26511088</t>
+  </si>
+  <si>
+    <t>B63RL26511412</t>
+  </si>
+  <si>
+    <t>2507566</t>
+  </si>
+  <si>
+    <t>36ZE110MD323R</t>
+  </si>
+  <si>
+    <t>RL26511412</t>
+  </si>
+  <si>
+    <t>B63RL26511413</t>
+  </si>
+  <si>
+    <t>2507568</t>
+  </si>
+  <si>
+    <t>36ZE750455D1R</t>
+  </si>
+  <si>
+    <t>RL26511413</t>
+  </si>
+  <si>
+    <t>B63RL26511414</t>
+  </si>
+  <si>
+    <t>2507569</t>
+  </si>
+  <si>
+    <t>36ZE750454D1R</t>
+  </si>
+  <si>
+    <t>RL26511414</t>
+  </si>
+  <si>
+    <t>B63RL26511416</t>
+  </si>
+  <si>
+    <t>2507567</t>
+  </si>
+  <si>
+    <t>39ZE1713D1R</t>
+  </si>
+  <si>
+    <t>RL26511416</t>
+  </si>
+  <si>
+    <t>B63PO26508990</t>
+  </si>
+  <si>
+    <t>2497191</t>
+  </si>
+  <si>
+    <t>170ZE2456D8</t>
+  </si>
+  <si>
+    <t>PO26508990</t>
+  </si>
+  <si>
+    <t>B63PO26509396</t>
+  </si>
+  <si>
+    <t>2497777</t>
+  </si>
+  <si>
+    <t>46ZE14601D32</t>
+  </si>
+  <si>
+    <t>PO26509396</t>
+  </si>
+  <si>
+    <t>B65RL26501786</t>
+  </si>
+  <si>
+    <t>2499575</t>
+  </si>
+  <si>
+    <t>1014541852U</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>RL26501786</t>
+  </si>
+  <si>
+    <t>B82RL26749017</t>
+  </si>
+  <si>
+    <t>2507377</t>
+  </si>
+  <si>
+    <t>3905 01303</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>RL26749017</t>
+  </si>
+  <si>
+    <t>B82RL26749054</t>
+  </si>
+  <si>
+    <t>2508282</t>
+  </si>
+  <si>
+    <t>8451 55</t>
+  </si>
+  <si>
+    <t>RL26749054</t>
+  </si>
+  <si>
+    <t>B82RL26749059</t>
+  </si>
+  <si>
+    <t>2507970</t>
+  </si>
+  <si>
+    <t>8451 46</t>
+  </si>
+  <si>
+    <t>RL26749059</t>
+  </si>
+  <si>
+    <t>B84RL26052745</t>
+  </si>
+  <si>
+    <t>2508283</t>
+  </si>
+  <si>
+    <t>1013290900</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>RL26052745</t>
+  </si>
+  <si>
+    <t>B84PO26051640</t>
+  </si>
+  <si>
+    <t>2502698</t>
+  </si>
+  <si>
+    <t>1014485133</t>
+  </si>
+  <si>
+    <t>PO26051640</t>
+  </si>
+  <si>
+    <t>B84PO26051716</t>
+  </si>
+  <si>
+    <t>2502669</t>
+  </si>
+  <si>
+    <t>PO26051716</t>
+  </si>
+  <si>
+    <t>B84PO26052315</t>
+  </si>
+  <si>
+    <t>2506997</t>
+  </si>
+  <si>
+    <t>1014320374</t>
+  </si>
+  <si>
+    <t>PO26052315</t>
+  </si>
+  <si>
+    <t>B85RL26616507</t>
+  </si>
+  <si>
+    <t>2503997</t>
+  </si>
+  <si>
+    <t>8538 00278</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>RL26616507</t>
+  </si>
+  <si>
+    <t>B85PO26616599</t>
+  </si>
+  <si>
+    <t>2507958</t>
+  </si>
+  <si>
+    <t>1014394515</t>
+  </si>
+  <si>
+    <t>PO26616599</t>
+  </si>
+  <si>
+    <t>B85PO26616601</t>
+  </si>
+  <si>
+    <t>2507972</t>
+  </si>
+  <si>
+    <t>1014394519</t>
+  </si>
+  <si>
+    <t>PO26616601</t>
+  </si>
+  <si>
+    <t>B85PO26616602</t>
+  </si>
+  <si>
+    <t>2507964</t>
+  </si>
+  <si>
+    <t>1014394521</t>
+  </si>
+  <si>
+    <t>PO26616602</t>
+  </si>
+  <si>
+    <t>BAZRL26140324</t>
+  </si>
+  <si>
+    <t>2501099</t>
+  </si>
+  <si>
+    <t>1014227567</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>RL26140324</t>
+  </si>
+  <si>
+    <t>BAZPO26140308</t>
+  </si>
+  <si>
+    <t>2502689</t>
+  </si>
+  <si>
+    <t>57S5712000</t>
+  </si>
+  <si>
+    <t>PO26140308</t>
+  </si>
+  <si>
+    <t>C67RL26360808</t>
+  </si>
+  <si>
+    <t>2508445</t>
+  </si>
+  <si>
+    <t>84050098</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>RL26360808</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,7 +970,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -133,12 +978,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,9 +1335,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B01D7E-9741-4D75-B0F4-F372D4AABE30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -493,24 +1356,24 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -523,43 +1386,1443 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>101</v>
+      </c>
+      <c r="F36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" t="s">
+        <v>197</v>
+      </c>
+      <c r="F49" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" t="s">
+        <v>202</v>
+      </c>
+      <c r="F50" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F51" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" t="s">
+        <v>207</v>
+      </c>
+      <c r="F52" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" t="s">
+        <v>207</v>
+      </c>
+      <c r="F53" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
+        <v>207</v>
+      </c>
+      <c r="F54" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>207</v>
+      </c>
+      <c r="F55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>207</v>
+      </c>
+      <c r="F57" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>207</v>
+      </c>
+      <c r="F58" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
+        <v>244</v>
+      </c>
+      <c r="F60" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>249</v>
+      </c>
+      <c r="F61" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" t="s">
+        <v>249</v>
+      </c>
+      <c r="F62" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" t="s">
+        <v>249</v>
+      </c>
+      <c r="F63" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>262</v>
+      </c>
+      <c r="F64" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" t="s">
+        <v>262</v>
+      </c>
+      <c r="F65" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" t="s">
+        <v>262</v>
+      </c>
+      <c r="F66" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" t="s">
+        <v>262</v>
+      </c>
+      <c r="F67" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" t="s">
+        <v>278</v>
+      </c>
+      <c r="F68" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" t="s">
+        <v>278</v>
+      </c>
+      <c r="F69" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" t="s">
+        <v>278</v>
+      </c>
+      <c r="F70" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" t="s">
+        <v>278</v>
+      </c>
+      <c r="F71" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" t="s">
+        <v>295</v>
+      </c>
+      <c r="F72" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>295</v>
+      </c>
+      <c r="F73" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D74" t="s">
+        <v>304</v>
+      </c>
+      <c r="E74" t="s">
+        <v>305</v>
+      </c>
+      <c r="F74" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/LoginCPARS/Login-CPARS/Input/Ford Receiving - Input.xlsx
+++ b/LoginCPARS/Login-CPARS/Input/Ford Receiving - Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skrishnan1\Videos\Proj\LoginCPARS\Login-CPARS\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70446DA-4D1D-4217-8EAF-BB01F1361592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AC87E1-AAB9-44C5-BFC8-8A05674CFA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
